--- a/output/pdf_financials_xlsx/APR.UN.xlsx
+++ b/output/pdf_financials_xlsx/APR.UN.xlsx
@@ -2953,28 +2953,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>2.914</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.492</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.993</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>3.332</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>3.757</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>4.136</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>17.625</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>26.249</v>
+        <v>-5.387</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>26.249</v>
@@ -5391,34 +5391,34 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
+        <v>-0.585</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0</v>
+        <v>-0.166</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-0.611</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0</v>
+        <v>-2.117</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0</v>
+        <v>-0.407</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>-0.871</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-1.288</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0</v>
+        <v>-0.678</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0</v>
+        <v>-2.039</v>
       </c>
     </row>
     <row r="129">
@@ -10154,7 +10154,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>-0.585</v>
       </c>
@@ -14166,7 +14170,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>17.625</v>
       </c>
